--- a/submission/knowledge/A03-武汉非遗文化官/武汉非遗文化官QA导入表.xlsx
+++ b/submission/knowledge/A03-武汉非遗文化官/武汉非遗文化官QA导入表.xlsx
@@ -367,6 +367,601 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼传说和现在的楼？</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">传说是国家级非遗；今楼是重建后的公园。可以讲诗和故事，不要说唐楼原物仍在。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">传说</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉剧今晚有吗？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">场次看汉剧院和文旅公告。我不编今晚必演。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哪里听湖北大鼓？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以保护单位和展演公告为准，不是景区附赠。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杖头木偶算武汉非遗吗？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武汉杖头木偶戏是公开报道过的非遗项目，与晴川阁夜游结合过。场次问预约官。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木偶</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">归元庙会哪天？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">香期看寺院和政府通告，不是每天都按庙会规模。入寺规则另问讲解员。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">庙会</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">花木兰是武汉人吗？</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木兰传说是国家级非遗，流布与黄陂等相关。不要把电影情节当户籍档案。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">热干面是非遗吗？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">制作技艺是省级非遗。哪家更好吃问美食顾问，我不排名。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">热干面</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最正宗在哪？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看公示老字号和有证店。文化官不点网红榜。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正宗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能在古琴台摔琴拍照吗？</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要戏说恶搞。周一常闭，进门问讲解员。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古琴台</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听楚剧要注意什么？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">准时噤声。场次看剧院公告。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能预约汉绣课吗？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看保护单位公告。购票问商户助手。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体验</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湖北评书是武汉非遗吗？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湖北省非遗网将湖北评书列为武汉市国家级项目之一。场次看保护单位公告。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">名录</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湖北小曲呢？</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同样出现在武汉市国家级曲艺类项目中。不是景区大门票附赠节目。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">名录</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">京剧算武汉发明的吗？</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">名录里有京剧保护单位在汉申报，不要讲成武汉发明了京剧。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">名录</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣保护单位是谁？</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中国非遗网载申报地武汉市江汉区，保护单位武汉市江汉区文化馆。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能点名传承人吗？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公开名录有黄圣辉等。不承诺此刻在某店表演。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣和苏绣有什么不同？</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣公开简介强调花无正果、热闹为先、楚风浓艳。不要贬低其他绣种。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能教我绣一朵吗？</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体验课看保护单位公告。我不代售课程。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古琴台今天开吗？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">开放问景点讲解员。我只讲伯牙子期传说，惯例周一常闭。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知音</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">空间名和灯笼有关吗？</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无关。江城是武汉别称，知音来自伯牙子期传说。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知音</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过早是国家级非遗吗？</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公开口径里「武汉过早」常见于市级名录。热干面制作技艺是省级。点单问美食顾问。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过早</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔡林记门店你报吗？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不报。那是美食顾问的范围。我只讲技艺名录属性。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过早</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">楚剧汉剧哪个更好听？</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">都是国家级剧种，声腔不同。我不排名。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">楚剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听不懂方言怎么办？</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看字幕，不嘲笑。场次看武汉楚剧院公告。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">楚剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">花木兰电影能当史实讲吗？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。木兰传说是口头传统，流布与黄陂等相关，不要把影视当户籍档案。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木兰</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">归元寺门票你讲吗？</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入寺规则问讲解员或商户助手。我讲庙会作为国家级非遗的礼仪，不推销高香。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">庙会</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼哪一层是非遗？</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">非遗是传说系统，不是某一层展柜。今楼是1985年重建。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">传说</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知音号是非遗吗？</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">那是当代游船产品。非遗是伯牙子期传说。票务问预约官。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参观汉绣要穿汉服吗？</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不强制。安静、不摸展品、先问能否拍照即可。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">礼仪</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能录音录像吗？</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先看场馆规定。戏剧演出默认关闪光灯。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">礼仪</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杖头木偶今晚在晴川阁吗？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉阳区报道曾结合夜游演出。是否仍演问预约官，我不编今晚场次。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木偶</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">马应龙能帮我开药吗？</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。只介绍「中医传统制剂方法（马应龙制药技艺）」名录属性。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医药</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">琴台音乐厅的音乐会是非遗吗？</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">那是当代演出场所。与古琴台景区门票、伯牙子期传说都不是同一套。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我排去黄陂看木兰的一天。</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">跨区结构问行程规划师。我只讲木兰传说。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼要买票吗？</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进出规则问景点讲解员。我讲传说，不报票价。</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>